--- a/云安全-课程报告-评分模板.xlsx
+++ b/云安全-课程报告-评分模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repo\ReportProj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repo\GradeHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4AE308-2ADE-438C-A9E7-7FA04D3BB721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345FD32D-996D-4993-B0B5-D4735A05E1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B5495C8D-CE22-411A-AC44-2F70D15E6953}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{B5495C8D-CE22-411A-AC44-2F70D15E6953}"/>
   </bookViews>
   <sheets>
     <sheet name="rule" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t>评分项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,19 +170,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>总分(使用公式算分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>引导LLM给出评语和评分。评语要给出评分原因。+[0, 4]分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>引导LLM给出评语和评分。评语要给出评分原因。+[0, 15]分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>......</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -276,6 +268,26 @@
   </si>
   <si>
     <t>课程总结。根据描述清晰性、完整性、详略程度打分。课程的主体内容为云计算和云安全的相关基础知识；云计算相关的安全风险分析；主机虚拟化技术及安全分析；网络虚拟化及安全分析；身份管理及访问控制相关知识；云数据及其安全问题；docker相关知识及操作；NoSQL MongoDB SQLite hbase等相关知识；虚拟主机的配置及其网络配置。对课程的总结应落在这个范围，相关内容越多得分越高。也可以包含对云安全课程的收益、建议等。如果加入学习过程的亲身体会和经历，额外+2(不受上限15分的限制)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summary评分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summary置信度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summary评语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>......此处省略的列由rule表决定。......</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -689,7 +701,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>27</v>
@@ -709,7 +721,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
@@ -729,7 +741,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>29</v>
@@ -749,10 +761,10 @@
         <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
@@ -769,15 +781,15 @@
         <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -789,10 +801,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
@@ -809,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>30</v>
@@ -817,7 +829,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -829,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>31</v>
@@ -837,7 +849,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -849,7 +861,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>32</v>
@@ -869,10 +881,10 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="69" x14ac:dyDescent="0.25">
@@ -889,10 +901,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
@@ -909,10 +921,10 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
@@ -929,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
@@ -949,10 +961,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
@@ -969,10 +981,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -984,19 +996,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E28C07-EB01-45E0-8A07-CC91905DA993}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1007,22 +1024,31 @@
         <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>36</v>
+        <v>62</v>
+      </c>
+      <c r="J1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
